--- a/data/dividends_info_20260902.xlsx
+++ b/data/dividends_info_20260902.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>43.125</v>
+        <v>43.72000122070312</v>
       </c>
       <c r="I2" t="n">
-        <v>0.208695652173913</v>
+        <v>0.2058554379851698</v>
       </c>
       <c r="J2" t="n">
         <v>194</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>66.05000305175781</v>
+        <v>65.25</v>
       </c>
       <c r="I3" t="n">
-        <v>1.059803130442657</v>
+        <v>1.0727969348659</v>
       </c>
       <c r="J3" t="n">
         <v>173</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8.979999542236328</v>
+        <v>9.060000419616699</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6681514817210997</v>
+        <v>0.6622516249567504</v>
       </c>
       <c r="J4" t="n">
         <v>103</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>43.13000106811523</v>
+        <v>43.72000122070312</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2086714532138846</v>
+        <v>0.2058554379851698</v>
       </c>
       <c r="J6" t="n">
         <v>103</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>2.075000047683716</v>
+        <v>2.085000038146973</v>
       </c>
       <c r="I7" t="n">
-        <v>3.710843288218411</v>
+        <v>3.693045495981532</v>
       </c>
       <c r="J7" t="n">
         <v>82</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>23.69000053405762</v>
+        <v>23.80999946594238</v>
       </c>
       <c r="I8" t="n">
-        <v>1.139721375741795</v>
+        <v>1.13397734588867</v>
       </c>
       <c r="J8" t="n">
         <v>82</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>24.13999938964844</v>
+        <v>24.04999923706055</v>
       </c>
       <c r="I9" t="n">
-        <v>2.444076283833711</v>
+        <v>2.453222531046164</v>
       </c>
       <c r="J9" t="n">
         <v>82</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5.809999942779541</v>
+        <v>5.800000190734863</v>
       </c>
       <c r="I10" t="n">
-        <v>3.442340825640675</v>
+        <v>3.44827574867131</v>
       </c>
       <c r="J10" t="n">
         <v>75</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>10.28999996185303</v>
+        <v>10.32999992370605</v>
       </c>
       <c r="I11" t="n">
-        <v>4.470359588972856</v>
+        <v>4.453049403653505</v>
       </c>
       <c r="J11" t="n">
         <v>54</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>7.449999809265137</v>
+        <v>7.349999904632568</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8053691481358354</v>
+        <v>0.8163265412042129</v>
       </c>
       <c r="J12" t="n">
         <v>47</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5.039999961853027</v>
+        <v>5.099999904632568</v>
       </c>
       <c r="I15" t="n">
-        <v>0.753968259674922</v>
+        <v>0.7450980531486446</v>
       </c>
       <c r="J15" t="n">
         <v>26</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>23.69000053405762</v>
+        <v>23.80999946594238</v>
       </c>
       <c r="I16" t="n">
-        <v>1.139721375741795</v>
+        <v>1.13397734588867</v>
       </c>
       <c r="J16" t="n">
         <v>19</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1.980999946594238</v>
+        <v>1.983999967575073</v>
       </c>
       <c r="I17" t="n">
-        <v>2.877334757024864</v>
+        <v>2.872983917921519</v>
       </c>
       <c r="J17" t="n">
         <v>19</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>43.13000106811523</v>
+        <v>43.72000122070312</v>
       </c>
       <c r="I18" t="n">
-        <v>0.2086714532138846</v>
+        <v>0.2058554379851698</v>
       </c>
       <c r="J18" t="n">
         <v>19</v>
@@ -1322,10 +1322,10 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>92.80000305175781</v>
+        <v>95.05000305175781</v>
       </c>
       <c r="I19" t="n">
-        <v>1.433189608041513</v>
+        <v>1.399263500576399</v>
       </c>
       <c r="J19" t="n">
         <v>19</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>6.28000020980835</v>
+        <v>6.21999979019165</v>
       </c>
       <c r="I20" t="n">
-        <v>4.777069904097268</v>
+        <v>4.823151288092832</v>
       </c>
       <c r="J20" t="n">
         <v>12</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>2.440000057220459</v>
+        <v>2.380000114440918</v>
       </c>
       <c r="I22" t="n">
-        <v>9.016393231179443</v>
+        <v>9.243697034513792</v>
       </c>
       <c r="J22" t="n">
         <v>-23</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>5.039999961853027</v>
+        <v>5.099999904632568</v>
       </c>
       <c r="I23" t="n">
-        <v>0.753968259674922</v>
+        <v>0.7450980531486446</v>
       </c>
       <c r="J23" t="n">
         <v>-30</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2.519999980926514</v>
+        <v>2.599999904632568</v>
       </c>
       <c r="I25" t="n">
-        <v>5.871785758728343</v>
+        <v>5.69111559336426</v>
       </c>
       <c r="J25" t="n">
         <v>-30</v>
@@ -2024,7 +2024,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2075,7 +2075,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2092,7 +2092,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2102,14 +2102,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2119,14 +2119,14 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2143,7 +2143,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2160,7 +2160,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2177,7 +2177,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2187,14 +2187,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2211,7 +2211,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2221,14 +2221,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2245,7 +2245,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2262,7 +2262,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2279,7 +2279,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2296,7 +2296,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2313,7 +2313,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2330,7 +2330,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2347,7 +2347,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -2357,14 +2357,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2374,14 +2374,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2398,7 +2398,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2415,7 +2415,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2432,7 +2432,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2449,7 +2449,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2459,14 +2459,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2483,7 +2483,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2534,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>I GRANDI VIAGGI S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2544,14 +2544,14 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>I GRANDI VIAGGI S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -2721,7 +2721,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -2748,14 +2748,14 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2782,14 +2782,14 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2799,14 +2799,14 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -2857,7 +2857,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2935,7 +2935,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -2952,14 +2952,14 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Yakkyo S.p.A.</t>
+          <t>RT&amp;L S.P.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2976,7 +2976,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>RT&amp;L S.P.A.</t>
+          <t>Yakkyo S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3112,7 +3112,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>OLIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3129,7 +3129,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3139,14 +3139,14 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>OVS S.p.A.</t>
+          <t>Lindbergh S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3163,7 +3163,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3173,14 +3173,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>OLIDATA S.p.A.</t>
+          <t>OVS S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3214,7 +3214,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Lindbergh S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3333,7 +3333,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>JUVENTUS F.C. S.p.A.</t>
+          <t>rino petino S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3343,14 +3343,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3360,14 +3360,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>RES S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3384,7 +3384,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3418,7 +3418,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>RES S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3435,7 +3435,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3452,7 +3452,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>JUVENTUS F.C. S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3486,7 +3486,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>ELSA Solutions S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3554,7 +3554,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>rino petino S.p.A.</t>
+          <t>ELSA Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3673,7 +3673,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>BESTBE HOLDING S.p.A.</t>
+          <t>VINEXT S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3690,7 +3690,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>MIT SIM S.p.A.</t>
+          <t>gAIn360 S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3707,7 +3707,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3724,7 +3724,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>BESTBE HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3741,7 +3741,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Ecomembrane S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3758,7 +3758,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>DANIELI &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3768,14 +3768,14 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>DANIELI &amp; C. S.p.A.</t>
+          <t>MIT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3785,14 +3785,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3809,7 +3809,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3826,7 +3826,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Allcore S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3843,7 +3843,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>Allcore S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3877,7 +3877,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>VINEXT S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3894,7 +3894,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>Smart Capital S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3911,7 +3911,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Smart Capital S.p.A.</t>
+          <t>Ecomembrane S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3928,7 +3928,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>SIAV S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3938,14 +3938,14 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3962,7 +3962,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Predict S.p.A.</t>
+          <t>SIAV S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3972,14 +3972,14 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>gAIn360 S.p.A.</t>
+          <t>Predict S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3996,7 +3996,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -4013,7 +4013,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Guidotti Ships S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -4030,7 +4030,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>Edil San Felice S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -4040,14 +4040,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -4057,14 +4057,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Longino &amp; Cardenal S.p.A.</t>
+          <t>DBA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -4081,7 +4081,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -4098,7 +4098,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -4115,7 +4115,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -4125,14 +4125,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -4142,14 +4142,14 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
@@ -4183,7 +4183,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Metriks AI S.p.A. Società Benefit</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -4200,7 +4200,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -4217,7 +4217,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Guidotti Ships S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -4234,7 +4234,7 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -4251,7 +4251,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -4268,7 +4268,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -4285,7 +4285,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>Longino &amp; Cardenal S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4302,7 +4302,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Simone S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4319,7 +4319,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4336,7 +4336,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A.B.P. Nocivelli S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4346,14 +4346,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>Simone S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4370,7 +4370,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4387,7 +4387,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>Radici Pietro Industries &amp; Brands S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4404,7 +4404,7 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4421,7 +4421,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4438,7 +4438,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4455,7 +4455,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Triboo S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4472,7 +4472,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4489,7 +4489,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Telmes S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4506,7 +4506,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>Triboo S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4523,7 +4523,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Estrima S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4533,14 +4533,14 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>A.B.P. Nocivelli S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4550,14 +4550,14 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>Estrima S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4567,14 +4567,14 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>Telmes S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4591,7 +4591,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>DBA GROUP S.p.A.</t>
+          <t>Metriks AI S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4608,7 +4608,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4618,14 +4618,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4635,14 +4635,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Edil San Felice S.p.A. Società Benefit</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4659,7 +4659,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4676,7 +4676,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>Gens Aurea S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4693,7 +4693,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Grifal S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4710,7 +4710,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4720,14 +4720,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4737,14 +4737,14 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ETI S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4761,7 +4761,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>EPH INVEST S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4778,7 +4778,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>EPH INVEST S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4795,7 +4795,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>ETI S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4812,7 +4812,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4829,7 +4829,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4839,14 +4839,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4863,7 +4863,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4880,7 +4880,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4897,7 +4897,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4914,7 +4914,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>Franchi Umberto Marmi S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4931,7 +4931,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4948,7 +4948,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4965,7 +4965,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>NOTORIOUS PICTURES S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4982,7 +4982,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Monnalisa S.p.A.</t>
+          <t>Adventure S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4999,7 +4999,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Misitano &amp; Stracuzzi S.p.A.</t>
+          <t>Gambero Rosso S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -5016,7 +5016,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Magis S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -5033,7 +5033,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Lemon Sistemi S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -5050,7 +5050,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>International Care Company S.p.A.</t>
+          <t>Monnalisa S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5067,7 +5067,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>ISCC FINTECH S.p.A.</t>
+          <t>Misitano &amp; Stracuzzi S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5084,7 +5084,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Franchi Umberto Marmi S.p.A.</t>
+          <t>Magis S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5101,7 +5101,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Lemon Sistemi S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5118,7 +5118,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Adventure S.p.A.</t>
+          <t>International Care Company S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5135,7 +5135,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Rocket Sharing Company S.p.A.</t>
+          <t>ISCC FINTECH S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -5152,7 +5152,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Grifal S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -5169,7 +5169,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Gens Aurea S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -5186,7 +5186,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Gambero Rosso S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -5203,7 +5203,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -5220,7 +5220,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -5237,7 +5237,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -5254,7 +5254,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>Rocket Sharing Company S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -5271,7 +5271,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5288,7 +5288,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Reti S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5305,7 +5305,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>NOTORIOUS PICTURES S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5322,7 +5322,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5339,7 +5339,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5349,14 +5349,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5373,7 +5373,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Reti S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5390,7 +5390,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>Telesia S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -5407,7 +5407,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Telesia S.p.A.</t>
+          <t>TESSELLIS S.p.A.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5424,7 +5424,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>TESSELLIS S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -5441,7 +5441,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>BORGOSESIA S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5458,7 +5458,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>BORGOSESIA S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5475,7 +5475,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -5492,7 +5492,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5509,7 +5509,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5519,14 +5519,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -5543,7 +5543,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5560,7 +5560,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5577,7 +5577,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>CSP INTERNATIONAL FASHION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -5594,7 +5594,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -5611,7 +5611,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5628,7 +5628,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -5645,7 +5645,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -5662,7 +5662,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>OPT S.p.A.</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -5679,7 +5679,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>Dedem S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -5696,7 +5696,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>DESTINATION ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -5713,7 +5713,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Officina Stellare S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -5730,7 +5730,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>The Italian Sea Group S.p.A.</t>
+          <t>Dipietro Group S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -5740,14 +5740,14 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Tenax International S.p.A.</t>
+          <t>Alia Mentis S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -5764,7 +5764,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -5781,7 +5781,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -5798,7 +5798,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>B.F. S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -5815,7 +5815,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -5832,7 +5832,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -5849,7 +5849,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>Cogefeed S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -5866,7 +5866,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -5883,7 +5883,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>Cube Labs S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -5900,7 +5900,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>B.F. S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -5917,7 +5917,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>DEODATO.GALLERY S.p.A.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -5934,7 +5934,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -5951,7 +5951,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -5961,14 +5961,14 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Alia Mentis S.p.A.</t>
+          <t>OPS ECOM S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -5978,14 +5978,14 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Dedem S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -6002,7 +6002,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>DESTINATION ITALIA S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -6019,7 +6019,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>DEODATO.GALLERY S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -6036,7 +6036,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Cube Labs S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -6053,7 +6053,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>Met.Extra Group S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -6070,7 +6070,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Cogefeed S.p.A.</t>
+          <t>The Italian Sea Group S.p.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -6080,14 +6080,14 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -6104,7 +6104,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -6121,7 +6121,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -6138,7 +6138,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -6155,7 +6155,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Leone Film Group S.p.A.</t>
+          <t>First Point S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -6172,7 +6172,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Racing Force S.p.A.</t>
+          <t>Finanza.tech S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -6182,14 +6182,14 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -6206,7 +6206,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -6223,7 +6223,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -6240,7 +6240,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>IDNTT S.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -6257,7 +6257,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>Racing Force S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -6267,14 +6267,14 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -6291,7 +6291,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -6301,14 +6301,14 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>Portobello S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -6325,7 +6325,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>Piu' Medical S.p.A.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -6342,7 +6342,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -6359,7 +6359,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -6376,7 +6376,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -6393,7 +6393,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -6410,7 +6410,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>First Point S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -6427,7 +6427,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Finanza.tech S.p.A. Società Benefit</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -6444,7 +6444,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -6461,7 +6461,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>Leone Film Group S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -6478,7 +6478,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Dipietro Group S.p.A.</t>
+          <t>MONDO TV FRANCE</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -6495,7 +6495,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>MEVIM S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -6512,7 +6512,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>OPS ECOM S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -6522,14 +6522,14 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -6546,7 +6546,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Portobello S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -6563,7 +6563,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>Piu' Medical S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -6580,7 +6580,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -6597,7 +6597,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -6614,7 +6614,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>Tenax International S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -6631,7 +6631,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>OPT S.p.A.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -6648,7 +6648,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -6665,7 +6665,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>Officina Stellare S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -6682,7 +6682,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Matica Fintec S.p.A.</t>
+          <t>SG COMPANY SOCIETÀ BENEFIT S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -6699,7 +6699,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -6716,7 +6716,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>MONDO TV FRANCE</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -6733,7 +6733,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>MEVIM S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -6750,7 +6750,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>Matica Fintec S.p.A.</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -6767,7 +6767,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Met.Extra Group S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -6784,7 +6784,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>LANDI RENZO S.p.A.</t>
+          <t>S.S. Lazio S.p.A.</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -6794,7 +6794,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>SB Annual Report</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>S.S. Lazio S.p.A.</t>
+          <t>LANDI RENZO S.p.A.</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>SB Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -6856,78 +6856,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>OMER S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>SIAV S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Half Year Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>SIAV S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>